--- a/liste groupe 2.xlsx
+++ b/liste groupe 2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8976821-8C74-4346-ABA8-08B55B2E1115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD362D8-CD0C-4D89-B2F2-4761CB3A6244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 2.xlsx
+++ b/liste groupe 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD362D8-CD0C-4D89-B2F2-4761CB3A6244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A35F0B9-5712-4933-880A-4714CAE53020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 2.xlsx
+++ b/liste groupe 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A35F0B9-5712-4933-880A-4714CAE53020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD18543A-63D9-45E7-9588-FDCDAE6BABDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 2.xlsx
+++ b/liste groupe 2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD18543A-63D9-45E7-9588-FDCDAE6BABDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FFD521-3558-4F3B-932D-0CA2A6D7610D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 2.xlsx
+++ b/liste groupe 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FFD521-3558-4F3B-932D-0CA2A6D7610D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2EEC2C0-0754-4FF5-A6A4-DB648CF3391D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 2.xlsx
+++ b/liste groupe 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2EEC2C0-0754-4FF5-A6A4-DB648CF3391D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502ED3F8-E267-4AB3-B8D7-D7692EE37F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 2.xlsx
+++ b/liste groupe 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502ED3F8-E267-4AB3-B8D7-D7692EE37F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66F7DB2-64FF-49BF-8DD8-1A247CA40F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6960" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
